--- a/naver-place-crawler/results_health/수영구_PT.xlsx
+++ b/naver-place-crawler/results_health/수영구_PT.xlsx
@@ -423,7 +423,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>카엘</t>
+          <t>르에르 필라테스앤피티</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>yui017@naver.com</t>
+          <t>sunranan@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1425-8442</t>
+          <t>0507-1372-9606</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 724-1 6층</t>
+          <t>부산광역시 수영구 황령대로489번길 24 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lueur_pilapt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2012165021</t>
+          <t>2027523310</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2012165021</t>
+          <t>https://m.place.naver.com/place/2027523310</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미라클랜드휘트니스 남천점 헬스 PT</t>
+          <t>유니크짐 광안6호점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jsy_0426@naver.com</t>
+          <t>2017_uniquegym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1396-7774</t>
+          <t>051-757-1088</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로 60 2층 미라클랜드휘트니스</t>
+          <t>부산광역시 수영구 수영로545번길 21 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jsy_0426</t>
+          <t>https://uniquegym.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>32</v>
+        <v>522</v>
       </c>
       <c r="Q3" t="n">
-        <v>63</v>
+        <v>221</v>
       </c>
       <c r="R3" t="n">
-        <v>95</v>
+        <v>743</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1951656469</t>
+          <t>1089781029</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1951656469</t>
+          <t>https://m.place.naver.com/place/1089781029</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>프로필사진전문</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>쎈스튜디오 부산점</t>
+          <t>시스템짐 민락점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>yoondwkd@naver.com</t>
+          <t>sizeupp@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1444-0601</t>
+          <t>0507-1492-3235</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 무학로63번길 45-6 1층</t>
+          <t>부산광역시 수영구 광안해변로358번길 6 4층 시스템짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssen_busan</t>
+          <t>https://blog.naver.com/sizeupp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>162</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1809346445</t>
+          <t>1010471219</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1809346445</t>
+          <t>https://m.place.naver.com/place/1010471219</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KANG 바디케어센터</t>
+          <t>포드짐 광안점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kjhyjj@naver.com</t>
+          <t>fordgym-@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1379-2470</t>
+          <t>0507-1301-1516</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천바다로 26 602</t>
+          <t>부산광역시 수영구 수영로 586 MK메디컬빌딩 11, 12층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kjhyjj</t>
+          <t>https://www.instagram.com/fordgym_gwangan/?hl=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>747</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>389</v>
       </c>
       <c r="R5" t="n">
-        <v>14</v>
+        <v>1136</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1962214206</t>
+          <t>1439920963</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1962214206</t>
+          <t>https://m.place.naver.com/place/1439920963</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>핏핏바디트레이닝 PT센터 수영민락점</t>
+          <t>오루필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitfitness@naver.com</t>
+          <t>orupila@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1313-6660</t>
+          <t>0507-1384-6527</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 769 3층</t>
+          <t>부산광역시 수영구 광안로41번길 14 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitfitness</t>
+          <t>https://open.kakao.com/o/sdVRLamh</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
-        <v>414</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>569</v>
+        <v>26</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1289671813</t>
+          <t>1142137796</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1289671813</t>
+          <t>https://m.place.naver.com/place/1142137796</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>르에르 필라테스앤피티</t>
+          <t>클래식짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sunranan@naver.com</t>
+          <t>toaaud@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1372-9606</t>
+          <t>0507-1367-0412</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 황령대로489번길 24 5층</t>
+          <t>부산광역시 수영구 광일로 10 3층 클래식짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lueur_pilapt</t>
+          <t>http://www.instagram.com/bikini_t_lenny</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>530</v>
       </c>
       <c r="R7" t="n">
-        <v>27</v>
+        <v>548</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2027523310</t>
+          <t>1976607974</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2027523310</t>
+          <t>https://m.place.naver.com/place/1976607974</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shut up Squat</t>
+          <t>비해피휘트니스 수영점 헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>trainer0409@naver.com</t>
+          <t>vitamin1448@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>051-758-3020</t>
+          <t>051-757-7575</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 724-1</t>
+          <t>부산광역시 수영구 수영로 641 2층 비해피휘트니스 수영점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bul5252</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>423</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>532</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>955</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>38279584</t>
+          <t>1878819501</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38279584</t>
+          <t>https://m.place.naver.com/place/1878819501</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>달라스짐 더 프리미엄 헬스&amp;PT</t>
+          <t>오케이 피트니스 수영점 헬스PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dallasgympremium@naver.com</t>
+          <t>rlagurdks26291@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1322-7591</t>
+          <t>0507-1353-8674</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안해변로 292 2층 달라스짐 더 프리미엄</t>
+          <t>부산광역시 수영구 수영로741번길 12 현대아파트 B1층 오케이피트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dallasgym_the_premium</t>
+          <t>https://litt.ly/okfitness_24_suyeong</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>826</v>
+        <v>494</v>
       </c>
       <c r="Q9" t="n">
-        <v>1250</v>
+        <v>229</v>
       </c>
       <c r="R9" t="n">
-        <v>2076</v>
+        <v>723</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1792697479</t>
+          <t>1128413754</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792697479</t>
+          <t>https://m.place.naver.com/place/1128413754</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바론피티</t>
+          <t>큐브휘트니스 수영점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wousd9939@naver.com</t>
+          <t>kkddhh7336@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1340-9939</t>
+          <t>0507-1395-0251</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 381 지하1층</t>
+          <t>부산광역시 수영구 수영로 668 화목오피스텔 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wousd9939</t>
+          <t>https://www.instagram.com/cube_suyeong</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47</v>
+        <v>366</v>
       </c>
       <c r="Q10" t="n">
-        <v>204</v>
+        <v>414</v>
       </c>
       <c r="R10" t="n">
-        <v>251</v>
+        <v>780</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1199218179</t>
+          <t>1620523545</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1199218179</t>
+          <t>https://m.place.naver.com/place/1620523545</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에잇에잇 그룹PT</t>
+          <t>어나더짐 남천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>roi0890@naver.com</t>
+          <t>eunyoung928@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>070-8806-5888</t>
+          <t>0507-1360-9838</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 구락로 110 1층</t>
+          <t>부산광역시 수영구 수영로464번길 6 5층 어나더짐남천점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/88.functional_fit</t>
+          <t>http://www.instagram.com/anothergym_namcheon</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1458,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>173</v>
+        <v>835</v>
       </c>
       <c r="Q11" t="n">
-        <v>121</v>
+        <v>455</v>
       </c>
       <c r="R11" t="n">
-        <v>294</v>
+        <v>1290</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,51 +1482,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1481864298</t>
+          <t>1539393813</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481864298</t>
+          <t>https://m.place.naver.com/place/1539393813</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>핏튜브짐PT 민락점</t>
+          <t>벨로시티휘트니스&amp;PT 광안점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>velocity_gwangan@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1398-3830</t>
+          <t>0507-1401-6900</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 민락수변로 49 2동 215호 (민락동, KCC 하버뷰 상가)</t>
+          <t>부산광역시 수영구 수영로 631 파스텔라 스튜디오 2, 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/chelsea_gwangan/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="Q12" t="n">
-        <v>29</v>
+        <v>422</v>
       </c>
       <c r="R12" t="n">
-        <v>29</v>
+        <v>634</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,51 +1576,51 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1608769333</t>
+          <t>36266433</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1608769333</t>
+          <t>https://m.place.naver.com/place/36266433</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>유 피티 스튜디오</t>
+          <t>비해피휘트니스 광안역점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>coolrap1@naver.com</t>
+          <t>aor403@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1312-1156</t>
+          <t>0507-1363-2221</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 655 지하1층</t>
+          <t>부산광역시 수영구 장대골로 10 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/coolrap1</t>
+          <t>https://www.instagram.com/vhappy_fitness?igsh=MW5hcjJyZTdiaGd2Mw==</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>611</v>
       </c>
       <c r="Q13" t="n">
-        <v>427</v>
+        <v>334</v>
       </c>
       <c r="R13" t="n">
-        <v>428</v>
+        <v>945</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,51 +1670,51 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1986873743</t>
+          <t>1560721971</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1986873743</t>
+          <t>https://m.place.naver.com/place/1560721971</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SM 교정운동센터 남천점</t>
+          <t>팔로우핏</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>imn53300@naver.com</t>
+          <t>follow_fit@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1330-5330</t>
+          <t>0507-1434-7866</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로 65 2층</t>
+          <t>부산광역시 수영구 광안해변로 348 601호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://youtube.com//@SMC_busan</t>
+          <t>https://blog.naver.com/follow_fit</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1749,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q14" t="n">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="R14" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,51 +1764,51 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1760126913</t>
+          <t>1746922687</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1760126913</t>
+          <t>https://m.place.naver.com/place/1746922687</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>무브앤스웻 PT센터 수영점</t>
+          <t>인트로피트니스 망미점 연중무휴 24시 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>moveandsweat@naver.com</t>
+          <t>intro_fitness2@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1486-7926</t>
+          <t>0507-1423-9699</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 660 2층</t>
+          <t>부산광역시 수영구 과정로 54 새망미메디컬 7,8층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/moveandsweat</t>
+          <t>https://www.instagram.com/intro_fitness_mm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="Q15" t="n">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="R15" t="n">
-        <v>338</v>
+        <v>480</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,51 +1858,51 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1285220064</t>
+          <t>1371823623</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285220064</t>
+          <t>https://m.place.naver.com/place/1371823623</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>더바른 필라테스 망미점</t>
+          <t>젬스톤피트니스 수영남천점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>clbdch1@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1440-1521</t>
+          <t>0507-1434-1558</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 과정로 63 (센텀빌딩) 6층</t>
+          <t>부산광역시 수영구 수영로384번길 8 3층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thebareun_pilla?igsh=YnNnNzk5NGw3MDBz</t>
+          <t>https://gemstonefitness3.com</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>123</v>
+        <v>659</v>
       </c>
       <c r="Q16" t="n">
-        <v>89</v>
+        <v>442</v>
       </c>
       <c r="R16" t="n">
-        <v>212</v>
+        <v>1101</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,51 +1952,51 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1040025345</t>
+          <t>1732164309</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040025345</t>
+          <t>https://m.place.naver.com/place/1732164309</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>봄 필라테스</t>
+          <t>에잇에잇 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bom_ing__@naver.com</t>
+          <t>double79988@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1473-4570</t>
+          <t>070-4496-5888</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 475 2층</t>
+          <t>부산광역시 수영구 구락로 110 6층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://instagram.com/_bom_pilates</t>
+          <t>https://www.instagram.com/88.health_fit/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="Q17" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,51 +2046,51 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1372647186</t>
+          <t>1240239977</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1372647186</t>
+          <t>https://m.place.naver.com/place/1240239977</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>엔플로어</t>
+          <t>짐엔터 망미점 헬스PT&amp;GX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>enflore_@naver.com</t>
+          <t>sincret@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1414-7754</t>
+          <t>0507-1449-8810</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 과정로55번길 24-1 1층</t>
+          <t>부산광역시 수영구 과정로41번길 20 6,7층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_enflore</t>
+          <t>https://www.instagram.com/gymenter.official</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>268</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>488</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2068910111</t>
+          <t>1354372059</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2068910111</t>
+          <t>https://m.place.naver.com/place/1354372059</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2162,29 +2162,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>클래식짐</t>
+          <t>피티맵</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>toaaud@naver.com</t>
+          <t>pt-map@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1367-0412</t>
+          <t>0507-1306-8353</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광일로 10 3층 클래식짐</t>
+          <t>부산광역시 수영구 남천동로108번길 13 보광빌딩 2층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/bikini_t_lenny</t>
+          <t>https://www.instagram.com/ptmap8353/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>527</v>
+        <v>18</v>
       </c>
       <c r="R19" t="n">
-        <v>544</v>
+        <v>24</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1976607974</t>
+          <t>36160743</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976607974</t>
+          <t>https://m.place.naver.com/place/36160743</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>업스퀘트</t>
+          <t>힐링짐 PT센터 수영점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dran77@naver.com</t>
+          <t>healinggym95@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2269,12 +2269,12 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 724-1 7층 (광안동,상화빌딩)</t>
+          <t>부산광역시 수영구 연수로 399 7층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healinggym95</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2305,17 +2305,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>233</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>364</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,51 +2324,51 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1722046897</t>
+          <t>1645332186</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722046897</t>
+          <t>https://m.place.naver.com/place/1645332186</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>어나더짐 광안점</t>
+          <t>핏핏바디트레이닝 PT센터 수영민락점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>parkkr10116@naver.com</t>
+          <t>fitfitness@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1315-9838</t>
+          <t>0507-1313-6660</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로582번길 10 성원상떼빌 B1 어나더짐 광안점</t>
+          <t>부산광역시 수영구 수영로 769 3층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anothergym__gwangan</t>
+          <t>https://blog.naver.com/fitfitness</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>518</v>
+        <v>157</v>
       </c>
       <c r="Q21" t="n">
-        <v>380</v>
+        <v>416</v>
       </c>
       <c r="R21" t="n">
-        <v>898</v>
+        <v>573</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1737165951</t>
+          <t>1289671813</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737165951</t>
+          <t>https://m.place.naver.com/place/1289671813</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2440,30 +2440,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>밀도짐 광안점</t>
+          <t>어나더짐 광안점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mildo1@naver.com</t>
+          <t>parkkr10116@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1315-9838</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 무학로 46 지하1층</t>
+          <t>부산광역시 수영구 수영로582번길 10 성원상떼빌 B1 어나더짐 광안점</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s2xFXPfi</t>
+          <t>https://www.instagram.com/anothergym__gwangan</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2484,7 +2488,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2493,13 +2497,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>521</v>
       </c>
       <c r="Q22" t="n">
-        <v>54</v>
+        <v>380</v>
       </c>
       <c r="R22" t="n">
-        <v>68</v>
+        <v>901</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2512,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1836677643</t>
+          <t>1737165951</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1836677643</t>
+          <t>https://m.place.naver.com/place/1737165951</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2530,34 +2534,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>오루필라테스</t>
+          <t>하드코어필라테스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>orupila@naver.com</t>
+          <t>ybn3817@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1384-6527</t>
+          <t>0507-1481-1828</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안로41번길 14 2층</t>
+          <t>부산광역시 수영구 광일로 29 2층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sdVRLamh</t>
+          <t>https://www.instagram.com/hardcore_pilates_official</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2578,7 +2582,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2587,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,51 +2606,47 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1142137796</t>
+          <t>2073267828</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142137796</t>
+          <t>https://m.place.naver.com/place/2073267828</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>무예,격투기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>주짓수랩 남천</t>
+          <t>마빈짐 PT남천동본점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>knignthood00@naver.com</t>
+          <t>trainer_ju@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1412-4885</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로 38 7층 (스타빌딩)</t>
+          <t>부산광역시 수영구 남천동로 15 2층(남천동, 보우빌딩)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/knignthood00</t>
+          <t>https://blog.naver.com/trainer_ju</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="Q24" t="n">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="R24" t="n">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,51 +2696,47 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1191253111</t>
+          <t>1122143834</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1191253111</t>
+          <t>https://m.place.naver.com/place/1122143834</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>포드짐 광안점</t>
+          <t>웨이브짐 남천점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fordgym-@naver.com</t>
+          <t>martin_jung1127@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0507-1301-1516</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 586 MK메디컬빌딩 11, 12층</t>
+          <t>부산광역시 수영구 수영로 416</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fordgym_gwangan/?hl=ko</t>
+          <t>http://www.instagram.com/moopamakun</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2775,13 +2771,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>747</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>388</v>
+        <v>28</v>
       </c>
       <c r="R25" t="n">
-        <v>1135</v>
+        <v>31</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,47 +2786,51 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1439920963</t>
+          <t>1523410926</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1439920963</t>
+          <t>https://m.place.naver.com/place/1523410926</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>웨이브짐 남천점</t>
+          <t>내셔널팀피트니스 헬스장 &amp; PT 수영점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>martin_jung1127@naver.com</t>
+          <t>awdxasd@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1392-8113</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 416</t>
+          <t>부산광역시 수영구 수영로705번길 14 4층 내셔널팀 휘트니스 헬스장 수영점</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/moopamakun</t>
+          <t>https://www.instagram.com/ntf_suyeong</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2865,13 +2865,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>362</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>354</v>
       </c>
       <c r="R26" t="n">
-        <v>31</v>
+        <v>716</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2880,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1523410926</t>
+          <t>1886402536</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1523410926</t>
+          <t>https://m.place.naver.com/place/1886402536</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2902,29 +2902,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Y트레이닝센터</t>
+          <t>어게인 헬스 케어</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>wns8954@naver.com</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>vktk92v@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>againbodycare@gmail.com</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1368-7757</t>
+          <t>0507-1318-5648</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 황령대로 491 6층</t>
+          <t>부산광역시 수영구 수영로 765-1 5층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wns8954</t>
+          <t>https://youtube.com/@againbodycare</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2939,7 +2943,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2959,13 +2963,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>288</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>334</v>
+        <v>2</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2978,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1756645006</t>
+          <t>2032193779</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756645006</t>
+          <t>https://m.place.naver.com/place/2032193779</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2996,29 +3000,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>어나더짐 수영점</t>
+          <t>위드피트니스&amp;PT 남천점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>anothergym2@naver.com</t>
+          <t>with_namcheon@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1409-8588</t>
+          <t>0507-1350-6707</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 690-5 수영메디세움 3층, 4층 어나더짐수영점</t>
+          <t>부산광역시 수영구 광남로 35 위드피트니스 4,5층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anothergym2</t>
+          <t>https://blog.naver.com/with_namcheon</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3044,7 +3048,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3053,13 +3057,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>490</v>
+        <v>629</v>
       </c>
       <c r="Q28" t="n">
-        <v>436</v>
+        <v>1518</v>
       </c>
       <c r="R28" t="n">
-        <v>926</v>
+        <v>2147</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3072,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1958025040</t>
+          <t>1838300399</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958025040</t>
+          <t>https://m.place.naver.com/place/1838300399</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3090,29 +3094,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>어나더짐 남천점</t>
+          <t>리턴피티</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>eunyoung928@naver.com</t>
+          <t>jayoufitstudio@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1360-9838</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로464번길 6 5층 어나더짐남천점</t>
+          <t>부산광역시 수영구 수영로 724-1 6층 리턴피티 광안리 PT 수영점</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/anothergym_namcheon</t>
+          <t>https://www.instagram.com/return__pt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3147,13 +3147,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>835</v>
+        <v>11</v>
       </c>
       <c r="Q29" t="n">
-        <v>454</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>1289</v>
+        <v>13</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3162,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1539393813</t>
+          <t>2067713897</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539393813</t>
+          <t>https://m.place.naver.com/place/2067713897</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3184,34 +3184,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>알피짐피트니스 헬스&amp;PT 광안수영점</t>
+          <t>밀도짐 광안점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>rpgymfitness1@naver.com</t>
+          <t>mildo1@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1362-0567</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로652번길 6 정원센텀뷰 205호, 206호</t>
+          <t>부산광역시 수영구 무학로 46 지하1층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rpgymfitness_suyeong/?hl=ko</t>
+          <t>https://open.kakao.com/o/s2xFXPfi</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3221,7 +3217,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3232,7 +3228,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3241,13 +3237,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q30" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="R30" t="n">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3252,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2070987650</t>
+          <t>1836677643</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2070987650</t>
+          <t>https://m.place.naver.com/place/1836677643</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3278,29 +3274,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>시스템짐 민락점 헬스&amp;PT</t>
+          <t>바디랩</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sizeupp@naver.com</t>
+          <t>bodylab3594@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1492-3235</t>
+          <t>0507-1326-9679</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안해변로358번길 6 4층 시스템짐</t>
+          <t>부산광역시 수영구 광남로48번길 17 3층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sizeupp</t>
+          <t>http://cafe.naver.com/bodylab9679</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3331,17 +3327,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>92</v>
+        <v>367</v>
       </c>
       <c r="R31" t="n">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,17 +3346,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1010471219</t>
+          <t>37281908</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010471219</t>
+          <t>https://m.place.naver.com/place/37281908</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3372,25 +3368,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>마빈짐 PT남천동본점</t>
+          <t>스파르타 PT &amp; 시크릿 필라테스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>trainer_ju@naver.com</t>
+          <t>sparta_gym@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1441-8386</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천동로 15 2층(남천동, 보우빌딩)</t>
+          <t>부산광역시 수영구 수영로618번길 4 성우이린타워 5층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trainer_ju</t>
+          <t>https://blog.naver.com/sparta_gym</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="Q32" t="n">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="R32" t="n">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,17 +3440,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1122143834</t>
+          <t>36631134</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1122143834</t>
+          <t>https://m.place.naver.com/place/36631134</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3462,34 +3462,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>바디랩</t>
+          <t>스파르타 광안2호점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>bodylab3594@naver.com</t>
+          <t>sparta_gym@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1326-9679</t>
+          <t>0507-1305-8386</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로48번길 17 3층</t>
+          <t>부산광역시 수영구 광안로 49-1 상생빌딩 3층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://cafe.naver.com/bodylab9679</t>
+          <t>https://www.instagram.com/sparta_secret</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3515,17 +3515,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="Q33" t="n">
-        <v>365</v>
+        <v>76</v>
       </c>
       <c r="R33" t="n">
-        <v>365</v>
+        <v>305</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,17 +3534,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>37281908</t>
+          <t>1686445947</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37281908</t>
+          <t>https://m.place.naver.com/place/1686445947</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3556,29 +3556,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>리치웰휘트니스 광안점</t>
+          <t>어나더짐 민락본점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>richwellfitness@naver.com</t>
+          <t>hyunmin617@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1311-2750</t>
+          <t>0507-1400-8586</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천바다로21번길 85</t>
+          <t>부산광역시 수영구 광안해변로 311 서희스타힐스 센텀프리모 2층 어나더짐민락본점</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/richwellfitness</t>
+          <t>https://blog.naver.com/hyunmin617</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3604,7 +3604,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>64</v>
+        <v>1016</v>
       </c>
       <c r="Q34" t="n">
-        <v>311</v>
+        <v>849</v>
       </c>
       <c r="R34" t="n">
-        <v>375</v>
+        <v>1865</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,51 +3628,51 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1087010137</t>
+          <t>36428464</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1087010137</t>
+          <t>https://m.place.naver.com/place/36428464</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>짐엔터 망미점 헬스PT&amp;GX</t>
+          <t>고앤고짐</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sincret@naver.com</t>
+          <t>tobirys@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1449-8810</t>
+          <t>0507-1353-0350</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 과정로41번길 20 6,7층</t>
+          <t>부산광역시 수영구 연수로 386 3층 고앤고짐</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymenter.official</t>
+          <t>https://www.instagram.com/goandgo_gym</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3707,13 +3707,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="Q35" t="n">
-        <v>263</v>
+        <v>63</v>
       </c>
       <c r="R35" t="n">
-        <v>481</v>
+        <v>154</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,51 +3722,51 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1354372059</t>
+          <t>1645006111</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354372059</t>
+          <t>https://m.place.naver.com/place/1645006111</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>유메짐PT 남천점</t>
+          <t>유니크짐남천점 24시헬스PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>2017_uniquegym@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1345-2634</t>
+          <t>051-622-1088</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천동로108번길 38 1동 3층</t>
+          <t>부산광역시 수영구 광남로 38 801호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://yumegym-mo.imweb.me/</t>
+          <t>https://uniquegym.co.kr/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3801,13 +3801,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>11</v>
+        <v>346</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>250</v>
       </c>
       <c r="R36" t="n">
-        <v>47</v>
+        <v>596</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,47 +3816,51 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2079448563</t>
+          <t>1791418442</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2079448563</t>
+          <t>https://m.place.naver.com/place/1791418442</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>힐링짐 PT센터 수영점</t>
+          <t>더바른 필라테스 망미점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>healinggym95@naver.com</t>
+          <t>clbdch1@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1440-1521</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 연수로 399 7층</t>
+          <t>부산광역시 수영구 과정로 63 (센텀빌딩) 6층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healinggym95</t>
+          <t>https://www.instagram.com/thebareun_pilla?igsh=YnNnNzk5NGw3MDBz</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3871,7 +3875,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3891,13 +3895,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="Q37" t="n">
-        <v>233</v>
+        <v>90</v>
       </c>
       <c r="R37" t="n">
-        <v>363</v>
+        <v>213</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3906,17 +3910,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1645332186</t>
+          <t>1040025345</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1645332186</t>
+          <t>https://m.place.naver.com/place/1040025345</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3928,29 +3932,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>민락PT</t>
+          <t>피티타임</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bodyboom_pt@naver.com</t>
+          <t>pttime01@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1445-0546</t>
+          <t>0507-1355-9857</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안해변로358번길 14 8층(민락동, 씨플렉스)</t>
+          <t>부산광역시 수영구 남천동로10번길 2 2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/pttime01</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3960,12 +3964,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3981,17 +3985,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="R38" t="n">
-        <v>97</v>
+        <v>196</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4000,51 +4004,51 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1044054451</t>
+          <t>1160623003</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044054451</t>
+          <t>https://m.place.naver.com/place/1160623003</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>고앤고짐</t>
+          <t>나아짐재활운동센터</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>tobirys@naver.com</t>
+          <t>naagym_rehab@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1353-0350</t>
+          <t>0507-1353-0589</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 연수로 386 3층 고앤고짐</t>
+          <t>부산광역시 수영구 수영로 457 3층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goandgo_gym</t>
+          <t>https://blog.naver.com/naagym_rehab</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4059,7 +4063,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4079,13 +4083,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="Q39" t="n">
-        <v>63</v>
+        <v>280</v>
       </c>
       <c r="R39" t="n">
-        <v>154</v>
+        <v>439</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4094,65 +4098,61 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1645006111</t>
+          <t>36175126</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1645006111</t>
+          <t>https://m.place.naver.com/place/36175126</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>메디앤컬필라테스 광안점</t>
+          <t>정석피트니스 수영점 헬스 PT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ss2ppl@naver.com</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>sample@sample.or.kr</t>
-        </is>
-      </c>
+          <t>standardpt2@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1360-3353</t>
+          <t>0507-1364-4896</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안로 21 3층 메디앤컬필라테스</t>
+          <t>부산광역시 수영구 수영로 701 선옥빌딩 2, 3층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://www.medincurl.com/</t>
+          <t>https://blog.naver.com/standardpt2</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4168,7 +4168,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>237</v>
+        <v>475</v>
       </c>
       <c r="Q40" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="R40" t="n">
-        <v>368</v>
+        <v>610</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4192,51 +4192,51 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1604870283</t>
+          <t>1050344461</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604870283</t>
+          <t>https://m.place.naver.com/place/1050344461</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>스포츠,레크레이션교육</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>스웻하우스 PT&amp;바레&amp;요가 수영점</t>
+          <t>레드마린짐 남천점 1대1 PT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ujeong0601@naver.com</t>
+          <t>redmarine_gym@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1387-6953</t>
+          <t>0507-1477-7234</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 연수로416번길 29 2층</t>
+          <t>부산광역시 수영구 수영로 411 5층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sweathouse.busan?igsh=MTVqYWtvYjc0N25jOQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/redmarine_gym</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4271,13 +4271,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="R41" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4286,51 +4286,51 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2058299297</t>
+          <t>2072584514</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058299297</t>
+          <t>https://m.place.naver.com/place/2072584514</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>버닝209 그룹PT 하이록스</t>
+          <t>굿짐남천점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>burning209@naver.com</t>
+          <t>tnals6029@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1315-9209</t>
+          <t>0507-1414-6558</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로 209 지하1층 BURNING209</t>
+          <t>부산광역시 수영구 수영로 465 5층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/burning209_official</t>
+          <t>https://blog.naver.com/tnals6029/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="R42" t="n">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4380,51 +4380,47 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1861353958</t>
+          <t>1150473595</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1861353958</t>
+          <t>https://m.place.naver.com/place/1150473595</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>나아짐재활운동센터</t>
+          <t>업스퀘트</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>naagym_rehab@naver.com</t>
+          <t>dran77@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1353-0589</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 457 3층</t>
+          <t>부산광역시 수영구 수영로 724-1 7층 (광안동,상화빌딩)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naagym_rehab</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4434,12 +4430,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4455,17 +4451,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>279</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>438</v>
+        <v>2</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,51 +4470,51 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>36175126</t>
+          <t>1722046897</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36175126</t>
+          <t>https://m.place.naver.com/place/1722046897</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 남천점</t>
+          <t>수영역 브랜드짐 PT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>brandgym_official@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1497-0887</t>
+          <t>0507-1354-6241</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로 33 3층</t>
+          <t>부산광역시 수영구 수영로 642 3층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uno_gym_1</t>
+          <t>https://www.youtube.com/@%EB%B8%8C%EB%9E%9C%EB%93%9C%EC%A7%90</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4553,13 +4549,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>568</v>
+        <v>136</v>
       </c>
       <c r="Q44" t="n">
-        <v>597</v>
+        <v>228</v>
       </c>
       <c r="R44" t="n">
-        <v>1165</v>
+        <v>364</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4568,51 +4564,51 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1259221586</t>
+          <t>1355172270</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259221586</t>
+          <t>https://m.place.naver.com/place/1355172270</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>스탠다드짐 헬스&amp;PT 남천점</t>
+          <t>Y트레이닝센터</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>standardgym@naver.com</t>
+          <t>wns8954@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1362-1827</t>
+          <t>0507-1368-7757</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 황령대로 497 1층</t>
+          <t>부산광역시 수영구 황령대로 491 6층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wns8954</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4622,12 +4618,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4643,17 +4639,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>166</v>
+        <v>46</v>
       </c>
       <c r="Q45" t="n">
-        <v>772</v>
+        <v>288</v>
       </c>
       <c r="R45" t="n">
-        <v>938</v>
+        <v>334</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4662,51 +4658,51 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1575112833</t>
+          <t>1756645006</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575112833</t>
+          <t>https://m.place.naver.com/place/1756645006</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,레크레이션교육</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>체리짐 PT 수영점</t>
+          <t>스웻하우스 PT&amp;바레&amp;요가 수영점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>cherrygym_pt@naver.com</t>
+          <t>ujeong0601@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1321-7555</t>
+          <t>0507-1387-6953</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 672 동광빌딩 3층</t>
+          <t>부산광역시 수영구 연수로416번길 29 2층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cherrygym_pt</t>
+          <t>https://www.instagram.com/sweathouse.busan?igsh=MTVqYWtvYjc0N25jOQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4721,7 +4717,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4732,7 +4728,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4741,13 +4737,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>217</v>
+        <v>10</v>
       </c>
       <c r="Q46" t="n">
-        <v>251</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>468</v>
+        <v>12</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4756,51 +4752,51 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1764720924</t>
+          <t>2058299297</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764720924</t>
+          <t>https://m.place.naver.com/place/2058299297</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>정석피트니스 수영점 헬스 PT</t>
+          <t>민락PT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>standardpt2@naver.com</t>
+          <t>gudtmdtn09@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1364-4896</t>
+          <t>0507-1445-0546</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 701 선옥빌딩 2, 3층</t>
+          <t>부산광역시 수영구 광안해변로358번길 14 8층(민락동, 씨플렉스)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standardpt2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4810,12 +4806,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4831,17 +4827,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>474</v>
+        <v>76</v>
       </c>
       <c r="Q47" t="n">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="R47" t="n">
-        <v>608</v>
+        <v>98</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4850,17 +4846,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1050344461</t>
+          <t>1044054451</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050344461</t>
+          <t>https://m.place.naver.com/place/1044054451</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4872,34 +4868,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>브리너스짐</t>
+          <t>미라클랜드휘트니스 남천점 헬스 PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dotorijieun@naver.com</t>
+          <t>jsy_0426@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1496-7781</t>
+          <t>0507-1396-7774</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천바다로 8 2층</t>
+          <t>부산광역시 수영구 광남로 60 2층 미라클랜드휘트니스</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sWkU5fUg</t>
+          <t>https://blog.naver.com/jsy_0426</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4909,7 +4905,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4920,7 +4916,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4929,13 +4925,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="R48" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4944,17 +4940,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1736450850</t>
+          <t>1951656469</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1736450850</t>
+          <t>https://m.place.naver.com/place/1951656469</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4966,29 +4962,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>젬스톤피트니스 수영남천점 헬스&amp;PT</t>
+          <t>로우짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>bodyflexgynks89@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1434-1558</t>
+          <t>051-761-1088</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로384번길 8 3층</t>
+          <t>부산광역시 수영구 수영로 577 11층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://gemstonefitness3.com</t>
+          <t>https://www.instagram.com/rawgym.official?igsh=ZHIxeTFqbDczZGVm&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5014,7 +5010,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5023,13 +5019,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>649</v>
+        <v>29</v>
       </c>
       <c r="Q49" t="n">
-        <v>443</v>
+        <v>14</v>
       </c>
       <c r="R49" t="n">
-        <v>1092</v>
+        <v>43</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5038,51 +5034,51 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1732164309</t>
+          <t>2035004699</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732164309</t>
+          <t>https://m.place.naver.com/place/2035004699</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>인트로피트니스 망미점 연중무휴 24시 헬스&amp;PT</t>
+          <t>카엘</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>intro_fitness2@naver.com</t>
+          <t>yui017@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1423-9699</t>
+          <t>0507-1425-8442</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 과정로 54 새망미메디컬 7,8층</t>
+          <t>부산광역시 수영구 수영로 724-1 6층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/intro_fitness_mm</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5092,7 +5088,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5113,17 +5109,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>497</v>
+        <v>0</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5132,51 +5128,51 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1371823623</t>
+          <t>2012165021</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1371823623</t>
+          <t>https://m.place.naver.com/place/2012165021</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>유니크짐남천점 24시헬스PT</t>
+          <t>유메짐PT 남천점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2017_uniquegym@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>051-622-1088</t>
+          <t>0507-1345-2634</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로 38 801호</t>
+          <t>부산광역시 수영구 남천동로108번길 38 1동 3층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://uniquegym.co.kr/</t>
+          <t>https://yumegym-mo.imweb.me/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5211,13 +5207,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>347</v>
+        <v>12</v>
       </c>
       <c r="Q51" t="n">
-        <v>248</v>
+        <v>41</v>
       </c>
       <c r="R51" t="n">
-        <v>595</v>
+        <v>53</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5226,17 +5222,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1791418442</t>
+          <t>2079448563</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791418442</t>
+          <t>https://m.place.naver.com/place/2079448563</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5248,29 +5244,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>도달짐 PT 남천점</t>
+          <t>어나더캠프 그룹PT 광안수영점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>dodal_offical@naver.com</t>
+          <t>anothercamp@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1388-6760</t>
+          <t>0507-1377-9838</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 389 상가동 213호 (스타벅스 2층)</t>
+          <t>부산광역시 수영구 수영로 632-1 2층 201호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dodal_official</t>
+          <t>https://blog.naver.com/anothercamp</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5285,7 +5281,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5296,7 +5292,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5305,13 +5301,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="Q52" t="n">
-        <v>188</v>
+        <v>59</v>
       </c>
       <c r="R52" t="n">
-        <v>297</v>
+        <v>227</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5320,56 +5316,56 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1750573434</t>
+          <t>1024331308</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1750573434</t>
+          <t>https://m.place.naver.com/place/1024331308</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>어게인 헬스 케어</t>
+          <t>브리너스짐</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>vktk92v@naver.com</t>
+          <t>dotorijieun@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1318-5648</t>
+          <t>0507-1496-7781</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 765-1 5층</t>
+          <t>부산광역시 수영구 남천바다로 8 2층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://www.againbody.com/</t>
+          <t>https://open.kakao.com/o/sWkU5fUg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5399,13 +5395,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5414,51 +5410,51 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2032193779</t>
+          <t>1736450850</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032193779</t>
+          <t>https://m.place.naver.com/place/1736450850</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>어나더캠프 그룹PT 광안수영점</t>
+          <t>우노짐 헬스&amp;PT 남천점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>anothercamp@naver.com</t>
+          <t>unogym_1@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1377-9838</t>
+          <t>0507-1497-0887</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 632-1 2층 201호</t>
+          <t>부산광역시 수영구 광남로 33 3층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anothercamp</t>
+          <t>https://www.instagram.com/uno_gym_1</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5473,7 +5469,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5484,7 +5480,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5493,13 +5489,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>167</v>
+        <v>571</v>
       </c>
       <c r="Q54" t="n">
-        <v>58</v>
+        <v>603</v>
       </c>
       <c r="R54" t="n">
-        <v>225</v>
+        <v>1174</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5508,17 +5504,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1024331308</t>
+          <t>1259221586</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024331308</t>
+          <t>https://m.place.naver.com/place/1259221586</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5530,29 +5526,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>피티타임</t>
+          <t>엔플로어</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>pttime01@naver.com</t>
+          <t>enflore_@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1355-9857</t>
+          <t>0507-1414-7754</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천동로10번길 2 2층</t>
+          <t>부산광역시 수영구 과정로55번길 24-1 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pttime01</t>
+          <t>https://www.instagram.com/_enflore</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5567,7 +5563,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5587,13 +5583,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>195</v>
+        <v>1</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5602,17 +5598,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1160623003</t>
+          <t>2068910111</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160623003</t>
+          <t>https://m.place.naver.com/place/2068910111</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5624,29 +5620,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>비해피휘트니스 수영점 헬스PT</t>
+          <t>테넌짐 광안점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>avex04@naver.com</t>
+          <t>tannengym@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>051-757-7575</t>
+          <t>0507-1449-0466</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 641 2층 비해피휘트니스 수영점</t>
+          <t>부산광역시 수영구 광안해변로 323 2층 테넌짐</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/tannengym</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5656,12 +5652,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5677,17 +5673,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="Q56" t="n">
-        <v>509</v>
+        <v>453</v>
       </c>
       <c r="R56" t="n">
-        <v>927</v>
+        <v>862</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5696,66 +5692,66 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1878819501</t>
+          <t>1782492863</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1878819501</t>
+          <t>https://m.place.naver.com/place/1782492863</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>오케이피트니스 광안점 헬스&amp;PT</t>
+          <t>엘에이피티 반려견 동반 PT센터</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>okfitness-gwangan@naver.com</t>
+          <t>coo135779@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1437-8867</t>
+          <t>0507-1424-0552</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안해변로 299 민락동씨랜드활어센터 4층</t>
+          <t>부산광역시 수영구 광남로48번길 5 3층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.okfitness.co.kr/</t>
+          <t>https://www.instagram.com/lapt_fitness_dogfriendly</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5766,7 +5762,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5775,13 +5771,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="Q57" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R57" t="n">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5790,51 +5786,47 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1994173425</t>
+          <t>1444679041</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994173425</t>
+          <t>https://m.place.naver.com/place/1444679041</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>킹콩짐 남천점</t>
+          <t>바레피플&amp;88PT 수영역점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0507-1423-5988</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천동로108번길 12 트윈스빌딩 5층</t>
+          <t>부산광역시 수영구 수영로 646 2층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/kingkonggym_namcheon</t>
+          <t>https://www.instagram.com/barrepeople_88pt/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5869,13 +5861,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>95</v>
+        <v>171</v>
       </c>
       <c r="Q58" t="n">
-        <v>458</v>
+        <v>12</v>
       </c>
       <c r="R58" t="n">
-        <v>553</v>
+        <v>183</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5884,17 +5876,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1868414176</t>
+          <t>1150292233</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868414176</t>
+          <t>https://m.place.naver.com/place/1150292233</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5906,29 +5898,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>벨로시티휘트니스&amp;PT 광안점</t>
+          <t>어나더짐 수영점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>velocity_gwangan@naver.com</t>
+          <t>anothergym2@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1401-6900</t>
+          <t>0507-1409-8588</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 631 파스텔라 스튜디오 2, 3층</t>
+          <t>부산광역시 수영구 수영로 690-5 수영메디세움 3층, 4층 어나더짐수영점</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chelsea_gwangan/</t>
+          <t>https://blog.naver.com/anothergym2</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5943,7 +5935,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5954,7 +5946,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5963,13 +5955,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>212</v>
+        <v>492</v>
       </c>
       <c r="Q59" t="n">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="R59" t="n">
-        <v>634</v>
+        <v>930</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5978,17 +5970,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>36266433</t>
+          <t>1958025040</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36266433</t>
+          <t>https://m.place.naver.com/place/1958025040</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6000,29 +5992,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>스파르타 PT &amp; 시크릿 필라테스</t>
+          <t>더라이프헬스PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sparta_gym@naver.com</t>
+          <t>thelife_health@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1441-8386</t>
+          <t>0507-1421-7853</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로618번길 4 성우이린타워 5층</t>
+          <t>부산광역시 수영구 광서로 33 강남사우나 5층 더라이프헬스PT</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sparta_gym</t>
+          <t>https://blog.naver.com/thelife_health</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6057,13 +6049,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>166</v>
+        <v>43</v>
       </c>
       <c r="Q60" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R60" t="n">
-        <v>287</v>
+        <v>162</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6072,56 +6064,56 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>36631134</t>
+          <t>1254006181</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36631134</t>
+          <t>https://m.place.naver.com/place/1254006181</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>프로필사진전문</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>수영역 브랜드짐 PT</t>
+          <t>쎈스튜디오 부산점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>brandgym_official@naver.com</t>
+          <t>yoondwkd@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1354-6241</t>
+          <t>0507-1444-0601</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 642 3층</t>
+          <t>부산광역시 수영구 무학로63번길 45-6 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@%EB%B8%8C%EB%9E%9C%EB%93%9C%EC%A7%90</t>
+          <t>https://www.instagram.com/ssen_busan</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6151,13 +6143,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>218</v>
+        <v>4</v>
       </c>
       <c r="R61" t="n">
-        <v>354</v>
+        <v>4</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6166,17 +6158,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1355172270</t>
+          <t>1809346445</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1355172270</t>
+          <t>https://m.place.naver.com/place/1809346445</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6188,29 +6180,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>엘에이피티 반려견 동반 PT센터</t>
+          <t>비기닝하루</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>coo135779@naver.com</t>
+          <t>beginning_haru@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1424-0552</t>
+          <t>0507-1364-5904</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로48번길 5 3층</t>
+          <t>부산광역시 수영구 남천바다로 34 5층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lapt_fitness_dogfriendly</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6220,7 +6212,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6241,17 +6233,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="R62" t="n">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6260,17 +6252,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1444679041</t>
+          <t>1968869949</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1444679041</t>
+          <t>https://m.place.naver.com/place/1968869949</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6282,44 +6274,44 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>비해피휘트니스 광안역점</t>
+          <t>오케이피트니스 광안점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>aor403@naver.com</t>
+          <t>okfitness-gwangan@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1363-2221</t>
+          <t>0507-1437-8867</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 장대골로 10 1층</t>
+          <t>부산광역시 수영구 광안해변로 299 민락동씨랜드활어센터 4층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vhappy_fitness?igsh=MW5hcjJyZTdiaGd2Mw==</t>
+          <t>https://www.okfitness.co.kr/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6330,7 +6322,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6339,13 +6331,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>599</v>
+        <v>186</v>
       </c>
       <c r="Q63" t="n">
-        <v>314</v>
+        <v>102</v>
       </c>
       <c r="R63" t="n">
-        <v>913</v>
+        <v>288</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6354,51 +6346,51 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1560721971</t>
+          <t>1994173425</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1560721971</t>
+          <t>https://m.place.naver.com/place/1994173425</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>큐브휘트니스 수영점</t>
+          <t>에잇에잇 그룹PT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kkddhh7336@naver.com</t>
+          <t>suhyu_@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1395-0251</t>
+          <t>070-8806-5888</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 668 화목오피스텔 4층</t>
+          <t>부산광역시 수영구 구락로 110 1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cube_suyeong</t>
+          <t>https://www.instagram.com/88.functional_fit</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6424,7 +6416,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6433,13 +6425,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>365</v>
+        <v>173</v>
       </c>
       <c r="Q64" t="n">
-        <v>413</v>
+        <v>123</v>
       </c>
       <c r="R64" t="n">
-        <v>778</v>
+        <v>296</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6448,17 +6440,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1620523545</t>
+          <t>1481864298</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620523545</t>
+          <t>https://m.place.naver.com/place/1481864298</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6470,29 +6462,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>테넌짐 광안점</t>
+          <t>알피짐피트니스 헬스&amp;PT 광안수영점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>tannengym@naver.com</t>
+          <t>rpgymfitness1@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1449-0466</t>
+          <t>0507-1362-0567</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안해변로 323 2층 테넌짐</t>
+          <t>부산광역시 수영구 수영로652번길 6 정원센텀뷰 205호, 206호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tannengym</t>
+          <t>https://www.instagram.com/rpgymfitness_suyeong/?hl=ko</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6507,7 +6499,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6527,13 +6519,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>400</v>
+        <v>33</v>
       </c>
       <c r="Q65" t="n">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="R65" t="n">
-        <v>852</v>
+        <v>137</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6542,51 +6534,51 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1782492863</t>
+          <t>2070987650</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782492863</t>
+          <t>https://m.place.naver.com/place/2070987650</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>피트니스모건&amp;PT 수영민락본점</t>
+          <t>유 피티 스튜디오</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mogunfit@naver.com</t>
+          <t>coolrap1@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1389-5024</t>
+          <t>0507-1312-1156</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 민락수변로239번길 4 피트니스모건 1F, 2F</t>
+          <t>부산광역시 수영구 수영로 655 지하1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mogunfit</t>
+          <t>https://blog.naver.com/coolrap1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6621,13 +6613,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>213</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>288</v>
+        <v>428</v>
       </c>
       <c r="R66" t="n">
-        <v>501</v>
+        <v>429</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6636,17 +6628,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1232299387</t>
+          <t>1986873743</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1232299387</t>
+          <t>https://m.place.naver.com/place/1986873743</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6658,29 +6650,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>바라던PT</t>
+          <t>무브앤스웻 PT센터 수영점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>baradun_pt@naver.com</t>
+          <t>moveandsweat@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1485-5509</t>
+          <t>0507-1486-7926</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 650 3층</t>
+          <t>부산광역시 수영구 수영로 660 2층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baradun_pt</t>
+          <t>https://blog.naver.com/moveandsweat</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6711,17 +6703,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="Q67" t="n">
-        <v>52</v>
+        <v>290</v>
       </c>
       <c r="R67" t="n">
-        <v>72</v>
+        <v>342</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6730,51 +6722,51 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1332130997</t>
+          <t>1285220064</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332130997</t>
+          <t>https://m.place.naver.com/place/1285220064</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>스파르타 광안2호점</t>
+          <t>달라스짐 더 프리미엄 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sparta_gym@naver.com</t>
+          <t>dallasgympremium@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1305-8386</t>
+          <t>0507-1322-7591</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안로 49-1 상생빌딩 3층</t>
+          <t>부산광역시 수영구 광안해변로 292 2층 달라스짐 더 프리미엄</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sparta_secret</t>
+          <t>https://www.instagram.com/dallasgym_the_premium</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6800,7 +6792,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6809,13 +6801,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>228</v>
+        <v>829</v>
       </c>
       <c r="Q68" t="n">
-        <v>76</v>
+        <v>1271</v>
       </c>
       <c r="R68" t="n">
-        <v>304</v>
+        <v>2100</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6824,61 +6816,65 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1686445947</t>
+          <t>1792697479</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1686445947</t>
+          <t>https://m.place.naver.com/place/1792697479</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>어나더짐 민락본점</t>
+          <t>메디앤컬필라테스 광안점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>hyunmin617@naver.com</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>ss2ppl@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>sample@sample.or.kr</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1400-8586</t>
+          <t>0507-1360-3353</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안해변로 311 서희스타힐스 센텀프리모 2층 어나더짐민락본점</t>
+          <t>부산광역시 수영구 광안로 21 3층 메디앤컬필라테스</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyunmin617</t>
+          <t>http://www.medincurl.com/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6903,13 +6899,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1015</v>
+        <v>242</v>
       </c>
       <c r="Q69" t="n">
-        <v>845</v>
+        <v>130</v>
       </c>
       <c r="R69" t="n">
-        <v>1860</v>
+        <v>372</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6918,56 +6914,56 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>36428464</t>
+          <t>1604870283</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428464</t>
+          <t>https://m.place.naver.com/place/1604870283</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>유니크짐 수영점</t>
+          <t>봄 필라테스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2017_uniquegym@naver.com</t>
+          <t>bom_ing__@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>051-755-1088</t>
+          <t>0507-1473-4570</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광일로 49 109동 지하층 상가103호</t>
+          <t>부산광역시 수영구 수영로 475 2층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://uniquegym.co.kr/</t>
+          <t>http://instagram.com/_bom_pilates</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6977,7 +6973,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6997,13 +6993,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>272</v>
+        <v>99</v>
       </c>
       <c r="Q70" t="n">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="R70" t="n">
-        <v>441</v>
+        <v>146</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7012,51 +7008,51 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1123543359</t>
+          <t>1372647186</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1123543359</t>
+          <t>https://m.place.naver.com/place/1372647186</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>영어교육</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>김현피티영어학원</t>
+          <t>스탠다드짐 헬스&amp;PT 남천점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>panther119@naver.com</t>
+          <t>standardgym@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1405-7912</t>
+          <t>0507-1362-1827</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로408번길 35 4층 402호</t>
+          <t>부산광역시 수영구 황령대로 497 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://www.pt-english.com/</t>
+          <t>https://blog.naver.com/standardgym</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7071,7 +7067,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7087,17 +7083,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="Q71" t="n">
-        <v>111</v>
+        <v>777</v>
       </c>
       <c r="R71" t="n">
-        <v>153</v>
+        <v>943</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7106,51 +7102,51 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>32284929</t>
+          <t>1575112833</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32284929</t>
+          <t>https://m.place.naver.com/place/1575112833</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>영어교육</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>에잇에잇 헬스&amp;PT</t>
+          <t>김현피티영어학원</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>double79988@naver.com</t>
+          <t>panther119@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>070-4496-5888</t>
+          <t>0507-1405-7912</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 구락로 110 6층</t>
+          <t>부산광역시 수영구 수영로408번길 35 4층 402호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/88.health_fit/</t>
+          <t>http://www.pt-english.com/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7181,17 +7177,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="R72" t="n">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7200,51 +7196,51 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1240239977</t>
+          <t>32284929</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240239977</t>
+          <t>https://m.place.naver.com/place/32284929</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>하드코어필라테스</t>
+          <t>버닝209 그룹PT 하이록스</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>k_d_yeah@naver.com</t>
+          <t>burning209@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1481-1828</t>
+          <t>0507-1315-9209</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광일로 29 2층</t>
+          <t>부산광역시 수영구 광남로 209 지하1층 BURNING209</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hardcore_pilates_official</t>
+          <t>https://www.instagram.com/burning209_official</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7279,13 +7275,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="R73" t="n">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7294,17 +7290,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2073267828</t>
+          <t>1861353958</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2073267828</t>
+          <t>https://m.place.naver.com/place/1861353958</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7316,34 +7312,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>리본휘트니스 남천점 헬스&amp;PT 24시 연중무휴</t>
+          <t>유니크짐 수영점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>seoktrainer92@naver.com</t>
+          <t>2017_uniquegym@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1300-3567</t>
+          <t>051-755-1088</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 황령대로473번길 15 남천 엑슬루타워 지하1층 리본휘트니스</t>
+          <t>부산광역시 수영구 광일로 49 109동 지하층 상가103호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rebornfitness_official/</t>
+          <t>https://uniquegym.co.kr/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7353,7 +7349,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7373,13 +7369,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="Q74" t="n">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="R74" t="n">
-        <v>494</v>
+        <v>447</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7388,17 +7384,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>173414915</t>
+          <t>1123543359</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/173414915</t>
+          <t>https://m.place.naver.com/place/1123543359</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7410,25 +7406,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>리턴피티</t>
+          <t>체리짐 PT 수영점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jayoufitstudio@naver.com</t>
+          <t>cherrygym_pt@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1321-7555</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 724-1 6층 리턴피티 광안리 PT 수영점</t>
+          <t>부산광역시 수영구 수영로 672 동광빌딩 3층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/return__pt</t>
+          <t>https://blog.naver.com/cherrygym_pt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7454,7 +7454,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>11</v>
+        <v>221</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="R75" t="n">
-        <v>13</v>
+        <v>477</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7478,51 +7478,51 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2067713897</t>
+          <t>1764720924</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067713897</t>
+          <t>https://m.place.naver.com/place/1764720924</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>무예,격투기</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>비기닝하루</t>
+          <t>주짓수랩 남천</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>beginning_haru@naver.com</t>
+          <t>knignthood00@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1364-5904</t>
+          <t>0507-1412-4885</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천바다로 34 5층</t>
+          <t>부산광역시 수영구 광남로 38 7층 (스타빌딩)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/knignthood00</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7532,12 +7532,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7553,17 +7553,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q76" t="n">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="R76" t="n">
-        <v>29</v>
+        <v>274</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7572,17 +7572,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1968869949</t>
+          <t>1191253111</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968869949</t>
+          <t>https://m.place.naver.com/place/1191253111</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7594,29 +7594,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>팔로우핏</t>
+          <t>도달짐 PT 남천점</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>follow_fit@naver.com</t>
+          <t>dodal_offical@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1434-7866</t>
+          <t>0507-1388-6760</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안해변로 348 601호</t>
+          <t>부산광역시 수영구 수영로 389 상가동 213호 (스타벅스 2층)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/follow_fit</t>
+          <t>https://www.instagram.com/dodal_official</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7651,13 +7651,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="Q77" t="n">
-        <v>99</v>
+        <v>188</v>
       </c>
       <c r="R77" t="n">
-        <v>144</v>
+        <v>297</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7666,34 +7666,34 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1746922687</t>
+          <t>1750573434</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1746922687</t>
+          <t>https://m.place.naver.com/place/1750573434</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>바레피플&amp;88PT 수영역점</t>
+          <t>트렌드핏 PT 수영점</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>trendfit@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -7701,12 +7701,12 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 646 2층</t>
+          <t>부산광역시 수영구 연수로 423 2층 트렌드핏</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barrepeople_88pt/</t>
+          <t>https://blog.naver.com/trendfit</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="Q78" t="n">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="R78" t="n">
-        <v>178</v>
+        <v>493</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7756,56 +7756,56 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1150292233</t>
+          <t>1641711339</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150292233</t>
+          <t>https://m.place.naver.com/place/1641711339</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>오케이 피트니스 수영점 헬스PT</t>
+          <t>바론피티</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>rlagurdks26291@naver.com</t>
+          <t>wousd9939@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1353-8674</t>
+          <t>0507-1340-9939</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로741번길 12 현대아파트 B1층 오케이피트니스</t>
+          <t>부산광역시 수영구 수영로 381 지하1층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://litt.ly/okfitness_24_suyeong</t>
+          <t>https://blog.naver.com/wousd9939</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7835,13 +7835,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>481</v>
+        <v>47</v>
       </c>
       <c r="Q79" t="n">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="R79" t="n">
-        <v>708</v>
+        <v>251</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7850,51 +7850,51 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1128413754</t>
+          <t>1199218179</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128413754</t>
+          <t>https://m.place.naver.com/place/1199218179</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>내셔널팀피트니스 헬스장 &amp; PT 수영점</t>
+          <t>핏튜브짐PT 민락점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>awdxasd@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1392-8113</t>
+          <t>0507-1398-3830</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로705번길 14 4층 내셔널팀 휘트니스 헬스장 수영점</t>
+          <t>부산광역시 수영구 민락수변로 49 2동 215호 (민락동, KCC 하버뷰 상가)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ntf_suyeong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7925,17 +7925,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>363</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>354</v>
+        <v>29</v>
       </c>
       <c r="R80" t="n">
-        <v>717</v>
+        <v>29</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7944,17 +7944,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1886402536</t>
+          <t>1608769333</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886402536</t>
+          <t>https://m.place.naver.com/place/1608769333</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7966,29 +7966,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>위드피트니스&amp;PT 남천점</t>
+          <t>리치웰휘트니스 광안점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>with_namcheon@naver.com</t>
+          <t>richwellfitness@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1350-6707</t>
+          <t>0507-1311-2750</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로 35 위드피트니스 4,5층</t>
+          <t>부산광역시 수영구 남천바다로21번길 85</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/with_namcheon</t>
+          <t>https://blog.naver.com/richwellfitness</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8023,13 +8023,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>625</v>
+        <v>64</v>
       </c>
       <c r="Q81" t="n">
-        <v>1510</v>
+        <v>311</v>
       </c>
       <c r="R81" t="n">
-        <v>2135</v>
+        <v>375</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8038,51 +8038,51 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1838300399</t>
+          <t>1087010137</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1838300399</t>
+          <t>https://m.place.naver.com/place/1087010137</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>로우짐 헬스&amp;PT</t>
+          <t>킹콩짐 남천점</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>bodyflexgynks89@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>051-761-1088</t>
+          <t>0507-1423-5988</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 577 11층</t>
+          <t>부산광역시 수영구 남천동로108번길 12 트윈스빌딩 5층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rawgym.official?igsh=ZHIxeTFqbDczZGVm&amp;utm_source=qr</t>
+          <t>https://smartstore.naver.com/kingkonggym_namcheon</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8117,13 +8117,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="Q82" t="n">
-        <v>13</v>
+        <v>458</v>
       </c>
       <c r="R82" t="n">
-        <v>41</v>
+        <v>553</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8132,47 +8132,51 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2035004699</t>
+          <t>1868414176</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2035004699</t>
+          <t>https://m.place.naver.com/place/1868414176</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>트렌드핏 PT 수영점</t>
+          <t>리본휘트니스 남천점 헬스&amp;PT 24시 연중무휴</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>trendfit@naver.com</t>
+          <t>seoktrainer92@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1300-3567</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 연수로 423 2층 트렌드핏</t>
+          <t>부산광역시 수영구 황령대로473번길 15 남천 엑슬루타워 지하1층 리본휘트니스</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trendfit</t>
+          <t>https://www.instagram.com/rebornfitness_official/</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8187,7 +8191,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8207,13 +8211,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="Q83" t="n">
-        <v>355</v>
+        <v>302</v>
       </c>
       <c r="R83" t="n">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8222,17 +8226,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1641711339</t>
+          <t>173414915</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1641711339</t>
+          <t>https://m.place.naver.com/place/173414915</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8244,29 +8248,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>피티맵</t>
+          <t>Shut up Squat</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>pt-map@naver.com</t>
+          <t>trainer0409@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1306-8353</t>
+          <t>051-758-3020</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천동로108번길 13 보광빌딩 2층</t>
+          <t>부산광역시 수영구 수영로 724-1</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ptmap8353/</t>
+          <t>https://www.instagram.com/bul5252</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8301,13 +8305,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q84" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R84" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8316,51 +8320,51 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>36160743</t>
+          <t>38279584</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36160743</t>
+          <t>https://m.place.naver.com/place/38279584</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>굿짐남천점</t>
+          <t>SM 교정운동센터 남천점</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>tnals6029@naver.com</t>
+          <t>imn53300@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1414-6558</t>
+          <t>0507-1330-5330</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 465 5층</t>
+          <t>부산광역시 수영구 광남로 65 2층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tnals6029/</t>
+          <t>https://youtube.com//@SMC_busan</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8375,7 +8379,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8391,17 +8395,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="Q85" t="n">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="R85" t="n">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8410,17 +8414,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1150473595</t>
+          <t>1760126913</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150473595</t>
+          <t>https://m.place.naver.com/place/1760126913</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8432,29 +8436,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>더라이프헬스PT</t>
+          <t>바라던PT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>thelife_health@naver.com</t>
+          <t>baradun_pt@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1421-7853</t>
+          <t>0507-1485-5509</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광서로 33 강남사우나 5층 더라이프헬스PT</t>
+          <t>부산광역시 수영구 수영로 650 3층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thelife_health</t>
+          <t>https://blog.naver.com/baradun_pt</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8485,17 +8489,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="Q86" t="n">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="R86" t="n">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8504,17 +8508,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1254006181</t>
+          <t>1332130997</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1254006181</t>
+          <t>https://m.place.naver.com/place/1332130997</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8526,34 +8530,34 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>유니크짐 광안6호점</t>
+          <t>피트니스모건&amp;PT 수영민락본점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2017_uniquegym@naver.com</t>
+          <t>mogunfit@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>051-757-1088</t>
+          <t>0507-1389-5024</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로545번길 21 6층</t>
+          <t>부산광역시 수영구 민락수변로239번길 4 피트니스모건 1F, 2F</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://uniquegym.co.kr/</t>
+          <t>https://blog.naver.com/mogunfit</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8583,13 +8587,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>517</v>
+        <v>215</v>
       </c>
       <c r="Q87" t="n">
-        <v>213</v>
+        <v>289</v>
       </c>
       <c r="R87" t="n">
-        <v>730</v>
+        <v>504</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8598,51 +8602,51 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1089781029</t>
+          <t>1232299387</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089781029</t>
+          <t>https://m.place.naver.com/place/1232299387</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>레드마린짐 남천점 1대1 PT</t>
+          <t>KANG 바디케어센터</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>redmarine_gym@naver.com</t>
+          <t>kjhyjj@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1477-7234</t>
+          <t>0507-1379-2470</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 411 5층</t>
+          <t>부산광역시 수영구 남천바다로 26 602</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/redmarine_gym</t>
+          <t>https://blog.naver.com/kjhyjj</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8673,18 +8677,18 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P88" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>12</v>
+      </c>
+      <c r="R88" t="n">
         <v>14</v>
       </c>
-      <c r="Q88" t="n">
-        <v>43</v>
-      </c>
-      <c r="R88" t="n">
-        <v>57</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>X</t>
@@ -8692,17 +8696,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2072584514</t>
+          <t>1962214206</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072584514</t>
+          <t>https://m.place.naver.com/place/1962214206</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
